--- a/msk-papers/肌骨康复图文论文清单.xlsx
+++ b/msk-papers/肌骨康复图文论文清单.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'论文总表'!$A$1:$T$341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'论文总表'!$A$1:$V$341</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T341"/>
+  <dimension ref="A1:V341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -591,7 +591,9 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -687,10 +689,20 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>全文链接（PMC，可下载PDF）</t>
+          <t>全文网页（PMC）</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>PDF下载</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>开放获取许可</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>交叉主题</t>
         </is>
@@ -782,7 +794,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5065670/</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5065670/pdf/</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -870,7 +892,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9556688/</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9556688/pdf/</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -958,7 +990,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3497949/</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3497949/pdf/</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1046,7 +1088,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9283193/</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9283193/pdf/</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1134,7 +1186,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3435948/</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3435948/pdf/</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1222,7 +1284,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13357443/</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13357443/pdf/</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1310,7 +1382,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5337779/</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5337779/pdf/</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1398,7 +1480,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5421351/</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5421351/pdf/</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1486,7 +1578,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9174504/</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9174504/pdf/</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1574,7 +1676,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10668940/</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10668940/pdf/</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1662,7 +1774,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4766355/</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4766355/pdf/</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1750,7 +1872,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4877346/</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4877346/pdf/</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1838,7 +1970,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3965765/</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3965765/pdf/</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1926,7 +2068,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4330230/</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4330230/pdf/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2014,7 +2166,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13021313/</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13021313/pdf/</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2102,7 +2264,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13120847/</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13120847/pdf/</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2190,7 +2362,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9292555/</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9292555/pdf/</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2278,7 +2460,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4825212/</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4825212/pdf/</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2366,7 +2558,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8678645/</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8678645/pdf/</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2454,7 +2656,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4035494/</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4035494/pdf/</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2542,7 +2754,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5036340/</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5036340/pdf/</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2630,7 +2852,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6169255/</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6169255/pdf/</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2718,7 +2950,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8505589/</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8505589/pdf/</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2806,7 +3048,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6447645/</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6447645/pdf/</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2894,7 +3146,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3548664/</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3548664/pdf/</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2982,7 +3244,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7509698/</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr"/>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7509698/pdf/</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -3070,7 +3342,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8137781/</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8137781/pdf/</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -3158,7 +3440,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11064639/</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr"/>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11064639/pdf/</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -3246,7 +3538,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11374584/</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr"/>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11374584/pdf/</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -3334,7 +3636,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9789266/</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr"/>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9789266/pdf/</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -3422,7 +3734,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8160369/</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8160369/pdf/</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3510,7 +3832,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7509696/</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7509696/pdf/</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3598,7 +3930,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4567363/</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4567363/pdf/</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3686,7 +4028,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3137866/</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr"/>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3137866/pdf/</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3774,7 +4126,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC1705542/</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC1705542/pdf/</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3862,7 +4224,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8899241/</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8899241/pdf/</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3950,7 +4322,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6044221/</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6044221/pdf/</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -4038,7 +4420,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3548665/</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3548665/pdf/</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -4126,7 +4518,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4877356/</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4877356/pdf/</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -4214,7 +4616,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13128079/</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13128079/pdf/</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -4302,7 +4714,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10899560/</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr"/>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10899560/pdf/</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -4390,7 +4812,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10668931/</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr"/>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10668931/pdf/</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -4478,7 +4910,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8007494/</t>
         </is>
       </c>
-      <c r="T44" s="2" t="inlineStr"/>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8007494/pdf/</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -4566,7 +5008,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5814508/</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr"/>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5814508/pdf/</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4654,7 +5106,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12634293/</t>
         </is>
       </c>
-      <c r="T46" s="2" t="inlineStr"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12634293/pdf/</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4742,7 +5204,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3259357/</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr"/>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3259357/pdf/</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4830,7 +5302,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5265202/</t>
         </is>
       </c>
-      <c r="T48" s="2" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5265202/pdf/</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4918,7 +5400,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5600038/</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr"/>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5600038/pdf/</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -5006,7 +5498,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6832410/</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr">
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6832410/pdf/</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>解剖、关节注射</t>
         </is>
@@ -5098,7 +5600,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3193630/</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr"/>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3193630/pdf/</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -5186,7 +5698,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2904904/</t>
         </is>
       </c>
-      <c r="T52" s="2" t="inlineStr"/>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2904904/pdf/</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -5274,7 +5796,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11400706/</t>
         </is>
       </c>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11400706/pdf/</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -5362,7 +5894,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4579750/</t>
         </is>
       </c>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4579750/pdf/</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -5450,7 +5992,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12169939/</t>
         </is>
       </c>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12169939/pdf/</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -5538,7 +6090,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7509702/</t>
         </is>
       </c>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7509702/pdf/</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -5626,7 +6188,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10253229/</t>
         </is>
       </c>
-      <c r="T57" s="2" t="inlineStr">
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10253229/pdf/</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>关节注射</t>
         </is>
@@ -5718,7 +6290,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13379185/</t>
         </is>
       </c>
-      <c r="T58" s="2" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13379185/pdf/</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5806,7 +6388,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6206372/</t>
         </is>
       </c>
-      <c r="T59" s="2" t="inlineStr">
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6206372/pdf/</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>关节注射</t>
         </is>
@@ -5898,7 +6490,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6118107/</t>
         </is>
       </c>
-      <c r="T60" s="2" t="inlineStr"/>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6118107/pdf/</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5986,7 +6588,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5582693/</t>
         </is>
       </c>
-      <c r="T61" s="2" t="inlineStr"/>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5582693/pdf/</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -6074,7 +6686,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4877349/</t>
         </is>
       </c>
-      <c r="T62" s="2" t="inlineStr"/>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4877349/pdf/</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -6162,7 +6784,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3675257/</t>
         </is>
       </c>
-      <c r="T63" s="2" t="inlineStr"/>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3675257/pdf/</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -6250,7 +6882,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9900010/</t>
         </is>
       </c>
-      <c r="T64" s="2" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9900010/pdf/</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -6338,7 +6980,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7571514/</t>
         </is>
       </c>
-      <c r="T65" s="2" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7571514/pdf/</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -6426,7 +7078,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3675245/</t>
         </is>
       </c>
-      <c r="T66" s="2" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3675245/pdf/</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -6514,7 +7176,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7845568/</t>
         </is>
       </c>
-      <c r="T67" s="2" t="inlineStr"/>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7845568/pdf/</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -6602,7 +7274,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10857999/</t>
         </is>
       </c>
-      <c r="T68" s="2" t="inlineStr">
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10857999/pdf/</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>解剖</t>
         </is>
@@ -6694,7 +7376,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11355885/</t>
         </is>
       </c>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11355885/pdf/</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6782,7 +7474,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8166753/</t>
         </is>
       </c>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8166753/pdf/</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6870,7 +7572,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5265197/</t>
         </is>
       </c>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5265197/pdf/</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6958,7 +7670,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3781258/</t>
         </is>
       </c>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3781258/pdf/</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -7046,7 +7768,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8039832/</t>
         </is>
       </c>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8039832/pdf/</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -7134,7 +7866,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8039565/</t>
         </is>
       </c>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8039565/pdf/</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -7222,7 +7964,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11109999/</t>
         </is>
       </c>
-      <c r="T75" s="2" t="inlineStr"/>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11109999/pdf/</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -7310,7 +8062,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10216848/</t>
         </is>
       </c>
-      <c r="T76" s="2" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10216848/pdf/</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -7398,7 +8160,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6319113/</t>
         </is>
       </c>
-      <c r="T77" s="2" t="inlineStr"/>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6319113/pdf/</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -7486,7 +8258,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7431516/</t>
         </is>
       </c>
-      <c r="T78" s="2" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7431516/pdf/</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -7574,7 +8356,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6667521/</t>
         </is>
       </c>
-      <c r="T79" s="2" t="inlineStr"/>
+      <c r="T79" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6667521/pdf/</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -7662,7 +8454,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10545656/</t>
         </is>
       </c>
-      <c r="T80" s="2" t="inlineStr"/>
+      <c r="T80" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10545656/pdf/</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -7750,7 +8552,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7539263/</t>
         </is>
       </c>
-      <c r="T81" s="2" t="inlineStr"/>
+      <c r="T81" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7539263/pdf/</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -7838,7 +8650,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3505561/</t>
         </is>
       </c>
-      <c r="T82" s="2" t="inlineStr"/>
+      <c r="T82" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3505561/pdf/</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -7926,7 +8748,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9917960/</t>
         </is>
       </c>
-      <c r="T83" s="2" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9917960/pdf/</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -8014,7 +8846,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8100693/</t>
         </is>
       </c>
-      <c r="T84" s="2" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8100693/pdf/</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -8102,7 +8944,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4805622/</t>
         </is>
       </c>
-      <c r="T85" s="2" t="inlineStr"/>
+      <c r="T85" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4805622/pdf/</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -8190,7 +9042,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5883171/</t>
         </is>
       </c>
-      <c r="T86" s="2" t="inlineStr"/>
+      <c r="T86" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5883171/pdf/</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -8278,7 +9140,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3259340/</t>
         </is>
       </c>
-      <c r="T87" s="2" t="inlineStr"/>
+      <c r="T87" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3259340/pdf/</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -8366,7 +9238,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4656234/</t>
         </is>
       </c>
-      <c r="T88" s="2" t="inlineStr"/>
+      <c r="T88" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4656234/pdf/</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -8454,7 +9336,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445137/</t>
         </is>
       </c>
-      <c r="T89" s="2" t="inlineStr"/>
+      <c r="T89" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445137/pdf/</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -8542,7 +9434,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5265199/</t>
         </is>
       </c>
-      <c r="T90" s="2" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5265199/pdf/</t>
+        </is>
+      </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -8630,7 +9532,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13502444/</t>
         </is>
       </c>
-      <c r="T91" s="5" t="inlineStr"/>
+      <c r="T91" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13502444/pdf/</t>
+        </is>
+      </c>
+      <c r="U91" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -8718,7 +9630,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10625514/</t>
         </is>
       </c>
-      <c r="T92" s="5" t="inlineStr"/>
+      <c r="T92" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10625514/pdf/</t>
+        </is>
+      </c>
+      <c r="U92" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -8806,7 +9728,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7418857/</t>
         </is>
       </c>
-      <c r="T93" s="5" t="inlineStr"/>
+      <c r="T93" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7418857/pdf/</t>
+        </is>
+      </c>
+      <c r="U93" s="5" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -8890,7 +9822,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7048573/</t>
         </is>
       </c>
-      <c r="T94" s="5" t="inlineStr"/>
+      <c r="T94" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7048573/pdf/</t>
+        </is>
+      </c>
+      <c r="U94" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -8978,7 +9920,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6262579/</t>
         </is>
       </c>
-      <c r="T95" s="5" t="inlineStr"/>
+      <c r="T95" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6262579/pdf/</t>
+        </is>
+      </c>
+      <c r="U95" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -9066,7 +10018,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12071253/</t>
         </is>
       </c>
-      <c r="T96" s="5" t="inlineStr"/>
+      <c r="T96" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12071253/pdf/</t>
+        </is>
+      </c>
+      <c r="U96" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -9154,7 +10116,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5698379/</t>
         </is>
       </c>
-      <c r="T97" s="5" t="inlineStr"/>
+      <c r="T97" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5698379/pdf/</t>
+        </is>
+      </c>
+      <c r="U97" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -9242,7 +10214,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4867934/</t>
         </is>
       </c>
-      <c r="T98" s="5" t="inlineStr"/>
+      <c r="T98" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4867934/pdf/</t>
+        </is>
+      </c>
+      <c r="U98" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -9330,7 +10312,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13138511/</t>
         </is>
       </c>
-      <c r="T99" s="5" t="inlineStr"/>
+      <c r="T99" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13138511/pdf/</t>
+        </is>
+      </c>
+      <c r="U99" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -9418,7 +10410,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5888833/</t>
         </is>
       </c>
-      <c r="T100" s="5" t="inlineStr"/>
+      <c r="T100" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5888833/pdf/</t>
+        </is>
+      </c>
+      <c r="U100" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -9506,7 +10508,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6850211/</t>
         </is>
       </c>
-      <c r="T101" s="5" t="inlineStr"/>
+      <c r="T101" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6850211/pdf/</t>
+        </is>
+      </c>
+      <c r="U101" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
@@ -9594,7 +10606,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13121326/</t>
         </is>
       </c>
-      <c r="T102" s="5" t="inlineStr"/>
+      <c r="T102" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13121326/pdf/</t>
+        </is>
+      </c>
+      <c r="U102" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -9682,7 +10704,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5992113/</t>
         </is>
       </c>
-      <c r="T103" s="5" t="inlineStr"/>
+      <c r="T103" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5992113/pdf/</t>
+        </is>
+      </c>
+      <c r="U103" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -9770,7 +10802,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3460084/</t>
         </is>
       </c>
-      <c r="T104" s="5" t="inlineStr"/>
+      <c r="T104" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3460084/pdf/</t>
+        </is>
+      </c>
+      <c r="U104" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -9858,7 +10900,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12101240/</t>
         </is>
       </c>
-      <c r="T105" s="5" t="inlineStr"/>
+      <c r="T105" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12101240/pdf/</t>
+        </is>
+      </c>
+      <c r="U105" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
@@ -9946,7 +10998,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13652943/</t>
         </is>
       </c>
-      <c r="T106" s="5" t="inlineStr"/>
+      <c r="T106" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13652943/pdf/</t>
+        </is>
+      </c>
+      <c r="U106" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -10034,7 +11096,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8534780/</t>
         </is>
       </c>
-      <c r="T107" s="5" t="inlineStr"/>
+      <c r="T107" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8534780/pdf/</t>
+        </is>
+      </c>
+      <c r="U107" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
@@ -10122,7 +11194,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12051118/</t>
         </is>
       </c>
-      <c r="T108" s="5" t="inlineStr"/>
+      <c r="T108" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12051118/pdf/</t>
+        </is>
+      </c>
+      <c r="U108" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -10210,7 +11292,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13474172/</t>
         </is>
       </c>
-      <c r="T109" s="5" t="inlineStr"/>
+      <c r="T109" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13474172/pdf/</t>
+        </is>
+      </c>
+      <c r="U109" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
@@ -10298,7 +11390,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7669814/</t>
         </is>
       </c>
-      <c r="T110" s="5" t="inlineStr"/>
+      <c r="T110" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7669814/pdf/</t>
+        </is>
+      </c>
+      <c r="U110" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
@@ -10386,7 +11488,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9676305/</t>
         </is>
       </c>
-      <c r="T111" s="5" t="inlineStr"/>
+      <c r="T111" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9676305/pdf/</t>
+        </is>
+      </c>
+      <c r="U111" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
@@ -10474,7 +11586,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4710116/</t>
         </is>
       </c>
-      <c r="T112" s="5" t="inlineStr"/>
+      <c r="T112" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4710116/pdf/</t>
+        </is>
+      </c>
+      <c r="U112" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -10562,7 +11684,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12712078/</t>
         </is>
       </c>
-      <c r="T113" s="5" t="inlineStr"/>
+      <c r="T113" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12712078/pdf/</t>
+        </is>
+      </c>
+      <c r="U113" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
@@ -10650,7 +11782,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12661223/</t>
         </is>
       </c>
-      <c r="T114" s="5" t="inlineStr"/>
+      <c r="T114" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12661223/pdf/</t>
+        </is>
+      </c>
+      <c r="U114" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -10738,7 +11880,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11826301/</t>
         </is>
       </c>
-      <c r="T115" s="5" t="inlineStr"/>
+      <c r="T115" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11826301/pdf/</t>
+        </is>
+      </c>
+      <c r="U115" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
@@ -10826,7 +11978,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7966405/</t>
         </is>
       </c>
-      <c r="T116" s="5" t="inlineStr"/>
+      <c r="T116" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7966405/pdf/</t>
+        </is>
+      </c>
+      <c r="U116" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -10914,7 +12076,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2855022/</t>
         </is>
       </c>
-      <c r="T117" s="5" t="inlineStr"/>
+      <c r="T117" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2855022/pdf/</t>
+        </is>
+      </c>
+      <c r="U117" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
@@ -11002,7 +12174,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11605026/</t>
         </is>
       </c>
-      <c r="T118" s="5" t="inlineStr"/>
+      <c r="T118" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11605026/pdf/</t>
+        </is>
+      </c>
+      <c r="U118" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
@@ -11090,7 +12272,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6890913/</t>
         </is>
       </c>
-      <c r="T119" s="5" t="inlineStr"/>
+      <c r="T119" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6890913/pdf/</t>
+        </is>
+      </c>
+      <c r="U119" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
@@ -11178,7 +12370,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10494809/</t>
         </is>
       </c>
-      <c r="T120" s="5" t="inlineStr"/>
+      <c r="T120" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10494809/pdf/</t>
+        </is>
+      </c>
+      <c r="U120" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -11266,7 +12468,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7151198/</t>
         </is>
       </c>
-      <c r="T121" s="5" t="inlineStr"/>
+      <c r="T121" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7151198/pdf/</t>
+        </is>
+      </c>
+      <c r="U121" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
@@ -11354,7 +12566,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10008353/</t>
         </is>
       </c>
-      <c r="T122" s="5" t="inlineStr"/>
+      <c r="T122" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10008353/pdf/</t>
+        </is>
+      </c>
+      <c r="U122" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
@@ -11442,7 +12664,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13238815/</t>
         </is>
       </c>
-      <c r="T123" s="5" t="inlineStr"/>
+      <c r="T123" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13238815/pdf/</t>
+        </is>
+      </c>
+      <c r="U123" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
@@ -11530,7 +12762,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13490228/</t>
         </is>
       </c>
-      <c r="T124" s="5" t="inlineStr"/>
+      <c r="T124" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13490228/pdf/</t>
+        </is>
+      </c>
+      <c r="U124" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
@@ -11618,7 +12860,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9110434/</t>
         </is>
       </c>
-      <c r="T125" s="5" t="inlineStr"/>
+      <c r="T125" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9110434/pdf/</t>
+        </is>
+      </c>
+      <c r="U125" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
@@ -11706,7 +12958,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12178697/</t>
         </is>
       </c>
-      <c r="T126" s="5" t="inlineStr"/>
+      <c r="T126" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12178697/pdf/</t>
+        </is>
+      </c>
+      <c r="U126" s="5" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -11794,7 +13056,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6706366/</t>
         </is>
       </c>
-      <c r="T127" s="5" t="inlineStr"/>
+      <c r="T127" s="7" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6706366/pdf/</t>
+        </is>
+      </c>
+      <c r="U127" s="5" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
@@ -11882,7 +13154,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5621981/</t>
         </is>
       </c>
-      <c r="T128" s="8" t="inlineStr"/>
+      <c r="T128" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5621981/pdf/</t>
+        </is>
+      </c>
+      <c r="U128" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V128" s="8" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
@@ -11970,7 +13252,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5622412/</t>
         </is>
       </c>
-      <c r="T129" s="8" t="inlineStr"/>
+      <c r="T129" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5622412/pdf/</t>
+        </is>
+      </c>
+      <c r="U129" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
@@ -12058,7 +13350,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6624186/</t>
         </is>
       </c>
-      <c r="T130" s="8" t="inlineStr"/>
+      <c r="T130" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6624186/pdf/</t>
+        </is>
+      </c>
+      <c r="U130" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V130" s="8" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
@@ -12146,7 +13448,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5981180/</t>
         </is>
       </c>
-      <c r="T131" s="8" t="inlineStr"/>
+      <c r="T131" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5981180/pdf/</t>
+        </is>
+      </c>
+      <c r="U131" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
@@ -12234,7 +13546,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5710065/</t>
         </is>
       </c>
-      <c r="T132" s="8" t="inlineStr"/>
+      <c r="T132" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5710065/pdf/</t>
+        </is>
+      </c>
+      <c r="U132" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V132" s="8" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
@@ -12322,7 +13644,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9069856/</t>
         </is>
       </c>
-      <c r="T133" s="8" t="inlineStr"/>
+      <c r="T133" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9069856/pdf/</t>
+        </is>
+      </c>
+      <c r="U133" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
@@ -12410,7 +13742,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8335959/</t>
         </is>
       </c>
-      <c r="T134" s="8" t="inlineStr"/>
+      <c r="T134" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8335959/pdf/</t>
+        </is>
+      </c>
+      <c r="U134" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
@@ -12498,7 +13840,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6394192/</t>
         </is>
       </c>
-      <c r="T135" s="8" t="inlineStr"/>
+      <c r="T135" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6394192/pdf/</t>
+        </is>
+      </c>
+      <c r="U135" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
@@ -12586,7 +13938,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7917228/</t>
         </is>
       </c>
-      <c r="T136" s="8" t="inlineStr"/>
+      <c r="T136" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7917228/pdf/</t>
+        </is>
+      </c>
+      <c r="U136" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V136" s="8" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
@@ -12674,7 +14036,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7181439/</t>
         </is>
       </c>
-      <c r="T137" s="8" t="inlineStr"/>
+      <c r="T137" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7181439/pdf/</t>
+        </is>
+      </c>
+      <c r="U137" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
@@ -12762,7 +14134,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8072106/</t>
         </is>
       </c>
-      <c r="T138" s="8" t="inlineStr"/>
+      <c r="T138" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8072106/pdf/</t>
+        </is>
+      </c>
+      <c r="U138" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V138" s="8" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
@@ -12850,7 +14232,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5367576/</t>
         </is>
       </c>
-      <c r="T139" s="8" t="inlineStr"/>
+      <c r="T139" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5367576/pdf/</t>
+        </is>
+      </c>
+      <c r="U139" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
@@ -12938,7 +14330,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6132395/</t>
         </is>
       </c>
-      <c r="T140" s="8" t="inlineStr"/>
+      <c r="T140" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6132395/pdf/</t>
+        </is>
+      </c>
+      <c r="U140" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V140" s="8" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="n">
@@ -13026,7 +14428,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13436837/</t>
         </is>
       </c>
-      <c r="T141" s="8" t="inlineStr"/>
+      <c r="T141" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13436837/pdf/</t>
+        </is>
+      </c>
+      <c r="U141" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
@@ -13114,7 +14526,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2682408/</t>
         </is>
       </c>
-      <c r="T142" s="8" t="inlineStr"/>
+      <c r="T142" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2682408/pdf/</t>
+        </is>
+      </c>
+      <c r="U142" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V142" s="8" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n">
@@ -13202,7 +14624,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5590003/</t>
         </is>
       </c>
-      <c r="T143" s="8" t="inlineStr"/>
+      <c r="T143" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5590003/pdf/</t>
+        </is>
+      </c>
+      <c r="U143" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
@@ -13290,7 +14722,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7722946/</t>
         </is>
       </c>
-      <c r="T144" s="8" t="inlineStr"/>
+      <c r="T144" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7722946/pdf/</t>
+        </is>
+      </c>
+      <c r="U144" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="n">
@@ -13378,7 +14820,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13123396/</t>
         </is>
       </c>
-      <c r="T145" s="8" t="inlineStr"/>
+      <c r="T145" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13123396/pdf/</t>
+        </is>
+      </c>
+      <c r="U145" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="8" t="n">
@@ -13466,7 +14918,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6334875/</t>
         </is>
       </c>
-      <c r="T146" s="8" t="inlineStr"/>
+      <c r="T146" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6334875/pdf/</t>
+        </is>
+      </c>
+      <c r="U146" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V146" s="8" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="n">
@@ -13554,7 +15016,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6020263/</t>
         </is>
       </c>
-      <c r="T147" s="8" t="inlineStr"/>
+      <c r="T147" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6020263/pdf/</t>
+        </is>
+      </c>
+      <c r="U147" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
@@ -13642,7 +15114,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5788098/</t>
         </is>
       </c>
-      <c r="T148" s="8" t="inlineStr"/>
+      <c r="T148" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5788098/pdf/</t>
+        </is>
+      </c>
+      <c r="U148" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V148" s="8" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="n">
@@ -13730,7 +15212,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6221419/</t>
         </is>
       </c>
-      <c r="T149" s="8" t="inlineStr"/>
+      <c r="T149" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6221419/pdf/</t>
+        </is>
+      </c>
+      <c r="U149" s="8" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="8" t="n">
@@ -13818,7 +15310,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445254/</t>
         </is>
       </c>
-      <c r="T150" s="8" t="inlineStr"/>
+      <c r="T150" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445254/pdf/</t>
+        </is>
+      </c>
+      <c r="U150" s="8" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V150" s="8" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n">
@@ -13906,7 +15408,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10240601/</t>
         </is>
       </c>
-      <c r="T151" s="8" t="inlineStr"/>
+      <c r="T151" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10240601/pdf/</t>
+        </is>
+      </c>
+      <c r="U151" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
@@ -13994,7 +15506,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4035495/</t>
         </is>
       </c>
-      <c r="T152" s="8" t="inlineStr"/>
+      <c r="T152" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4035495/pdf/</t>
+        </is>
+      </c>
+      <c r="U152" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V152" s="8" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="n">
@@ -14082,7 +15604,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5644424/</t>
         </is>
       </c>
-      <c r="T153" s="8" t="inlineStr"/>
+      <c r="T153" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5644424/pdf/</t>
+        </is>
+      </c>
+      <c r="U153" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="n">
@@ -14170,7 +15702,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3051891/</t>
         </is>
       </c>
-      <c r="T154" s="8" t="inlineStr"/>
+      <c r="T154" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3051891/pdf/</t>
+        </is>
+      </c>
+      <c r="U154" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V154" s="8" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="n">
@@ -14258,7 +15800,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2744659/</t>
         </is>
       </c>
-      <c r="T155" s="8" t="inlineStr"/>
+      <c r="T155" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2744659/pdf/</t>
+        </is>
+      </c>
+      <c r="U155" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
@@ -14346,7 +15898,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5718794/</t>
         </is>
       </c>
-      <c r="T156" s="8" t="inlineStr"/>
+      <c r="T156" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5718794/pdf/</t>
+        </is>
+      </c>
+      <c r="U156" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V156" s="8" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="n">
@@ -14434,7 +15996,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10323914/</t>
         </is>
       </c>
-      <c r="T157" s="8" t="inlineStr"/>
+      <c r="T157" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10323914/pdf/</t>
+        </is>
+      </c>
+      <c r="U157" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="8" t="n">
@@ -14522,7 +16094,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6667981/</t>
         </is>
       </c>
-      <c r="T158" s="8" t="inlineStr"/>
+      <c r="T158" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6667981/pdf/</t>
+        </is>
+      </c>
+      <c r="U158" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V158" s="8" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="n">
@@ -14610,7 +16192,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6179077/</t>
         </is>
       </c>
-      <c r="T159" s="8" t="inlineStr"/>
+      <c r="T159" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6179077/pdf/</t>
+        </is>
+      </c>
+      <c r="U159" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="8" t="n">
@@ -14698,7 +16290,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5851437/</t>
         </is>
       </c>
-      <c r="T160" s="8" t="inlineStr"/>
+      <c r="T160" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5851437/pdf/</t>
+        </is>
+      </c>
+      <c r="U160" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="n">
@@ -14786,7 +16388,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5994620/</t>
         </is>
       </c>
-      <c r="T161" s="8" t="inlineStr"/>
+      <c r="T161" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5994620/pdf/</t>
+        </is>
+      </c>
+      <c r="U161" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="8" t="n">
@@ -14874,7 +16486,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8564931/</t>
         </is>
       </c>
-      <c r="T162" s="8" t="inlineStr"/>
+      <c r="T162" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8564931/pdf/</t>
+        </is>
+      </c>
+      <c r="U162" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V162" s="8" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="n">
@@ -14962,7 +16584,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8381447/</t>
         </is>
       </c>
-      <c r="T163" s="8" t="inlineStr"/>
+      <c r="T163" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8381447/pdf/</t>
+        </is>
+      </c>
+      <c r="U163" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="8" t="n">
@@ -15050,7 +16682,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8696766/</t>
         </is>
       </c>
-      <c r="T164" s="8" t="inlineStr"/>
+      <c r="T164" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8696766/pdf/</t>
+        </is>
+      </c>
+      <c r="U164" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V164" s="8" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n">
@@ -15138,7 +16780,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4306730/</t>
         </is>
       </c>
-      <c r="T165" s="8" t="inlineStr"/>
+      <c r="T165" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4306730/pdf/</t>
+        </is>
+      </c>
+      <c r="U165" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="8" t="n">
@@ -15226,7 +16878,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8517984/</t>
         </is>
       </c>
-      <c r="T166" s="8" t="inlineStr"/>
+      <c r="T166" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8517984/pdf/</t>
+        </is>
+      </c>
+      <c r="U166" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V166" s="8" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="n">
@@ -15314,7 +16976,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445094/</t>
         </is>
       </c>
-      <c r="T167" s="8" t="inlineStr"/>
+      <c r="T167" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445094/pdf/</t>
+        </is>
+      </c>
+      <c r="U167" s="8" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="8" t="n">
@@ -15402,7 +17074,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4718498/</t>
         </is>
       </c>
-      <c r="T168" s="8" t="inlineStr"/>
+      <c r="T168" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4718498/pdf/</t>
+        </is>
+      </c>
+      <c r="U168" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V168" s="8" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="n">
@@ -15490,7 +17172,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5792748/</t>
         </is>
       </c>
-      <c r="T169" s="8" t="inlineStr"/>
+      <c r="T169" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5792748/pdf/</t>
+        </is>
+      </c>
+      <c r="U169" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="8" t="n">
@@ -15578,7 +17270,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5794495/</t>
         </is>
       </c>
-      <c r="T170" s="8" t="inlineStr"/>
+      <c r="T170" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5794495/pdf/</t>
+        </is>
+      </c>
+      <c r="U170" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V170" s="8" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="n">
@@ -15666,7 +17368,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5794674/</t>
         </is>
       </c>
-      <c r="T171" s="8" t="inlineStr"/>
+      <c r="T171" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5794674/pdf/</t>
+        </is>
+      </c>
+      <c r="U171" s="8" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="8" t="n">
@@ -15754,7 +17466,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3620582/</t>
         </is>
       </c>
-      <c r="T172" s="8" t="inlineStr"/>
+      <c r="T172" s="10" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3620582/pdf/</t>
+        </is>
+      </c>
+      <c r="U172" s="8" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V172" s="8" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="n">
@@ -15842,7 +17564,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13234441/</t>
         </is>
       </c>
-      <c r="T173" s="11" t="inlineStr"/>
+      <c r="T173" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13234441/pdf/</t>
+        </is>
+      </c>
+      <c r="U173" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V173" s="11" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="n">
@@ -15930,7 +17662,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5920395/</t>
         </is>
       </c>
-      <c r="T174" s="11" t="inlineStr"/>
+      <c r="T174" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5920395/pdf/</t>
+        </is>
+      </c>
+      <c r="U174" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V174" s="11" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="n">
@@ -16018,7 +17760,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5017176/</t>
         </is>
       </c>
-      <c r="T175" s="11" t="inlineStr"/>
+      <c r="T175" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5017176/pdf/</t>
+        </is>
+      </c>
+      <c r="U175" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V175" s="11" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="n">
@@ -16106,7 +17858,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6598040/</t>
         </is>
       </c>
-      <c r="T176" s="11" t="inlineStr"/>
+      <c r="T176" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6598040/pdf/</t>
+        </is>
+      </c>
+      <c r="U176" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V176" s="11" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="n">
@@ -16194,7 +17956,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4763148/</t>
         </is>
       </c>
-      <c r="T177" s="11" t="inlineStr"/>
+      <c r="T177" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4763148/pdf/</t>
+        </is>
+      </c>
+      <c r="U177" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V177" s="11" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="n">
@@ -16282,7 +18054,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12341944/</t>
         </is>
       </c>
-      <c r="T178" s="11" t="inlineStr"/>
+      <c r="T178" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12341944/pdf/</t>
+        </is>
+      </c>
+      <c r="U178" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V178" s="11" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="n">
@@ -16370,7 +18152,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12341709/</t>
         </is>
       </c>
-      <c r="T179" s="11" t="inlineStr"/>
+      <c r="T179" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12341709/pdf/</t>
+        </is>
+      </c>
+      <c r="U179" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V179" s="11" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="n">
@@ -16454,7 +18246,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12341714/</t>
         </is>
       </c>
-      <c r="T180" s="11" t="inlineStr"/>
+      <c r="T180" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12341714/pdf/</t>
+        </is>
+      </c>
+      <c r="U180" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V180" s="11" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="n">
@@ -16542,7 +18344,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12345343/</t>
         </is>
       </c>
-      <c r="T181" s="11" t="inlineStr"/>
+      <c r="T181" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12345343/pdf/</t>
+        </is>
+      </c>
+      <c r="U181" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V181" s="11" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="n">
@@ -16630,7 +18442,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5027008/</t>
         </is>
       </c>
-      <c r="T182" s="11" t="inlineStr"/>
+      <c r="T182" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5027008/pdf/</t>
+        </is>
+      </c>
+      <c r="U182" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V182" s="11" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="n">
@@ -16718,7 +18540,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4510794/</t>
         </is>
       </c>
-      <c r="T183" s="11" t="inlineStr"/>
+      <c r="T183" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4510794/pdf/</t>
+        </is>
+      </c>
+      <c r="U183" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V183" s="11" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="n">
@@ -16806,7 +18638,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12317417/</t>
         </is>
       </c>
-      <c r="T184" s="11" t="inlineStr"/>
+      <c r="T184" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12317417/pdf/</t>
+        </is>
+      </c>
+      <c r="U184" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V184" s="11" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="n">
@@ -16894,7 +18736,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13495697/</t>
         </is>
       </c>
-      <c r="T185" s="11" t="inlineStr"/>
+      <c r="T185" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13495697/pdf/</t>
+        </is>
+      </c>
+      <c r="U185" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V185" s="11" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="n">
@@ -16982,7 +18834,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5033781/</t>
         </is>
       </c>
-      <c r="T186" s="11" t="inlineStr"/>
+      <c r="T186" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5033781/pdf/</t>
+        </is>
+      </c>
+      <c r="U186" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V186" s="11" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="n">
@@ -17070,7 +18932,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12336002/</t>
         </is>
       </c>
-      <c r="T187" s="11" t="inlineStr"/>
+      <c r="T187" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12336002/pdf/</t>
+        </is>
+      </c>
+      <c r="U187" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V187" s="11" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="n">
@@ -17158,7 +19030,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12329124/</t>
         </is>
       </c>
-      <c r="T188" s="11" t="inlineStr"/>
+      <c r="T188" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12329124/pdf/</t>
+        </is>
+      </c>
+      <c r="U188" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V188" s="11" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="n">
@@ -17246,7 +19128,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12335991/</t>
         </is>
       </c>
-      <c r="T189" s="11" t="inlineStr"/>
+      <c r="T189" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12335991/pdf/</t>
+        </is>
+      </c>
+      <c r="U189" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V189" s="11" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="n">
@@ -17334,7 +19226,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12342060/</t>
         </is>
       </c>
-      <c r="T190" s="11" t="inlineStr"/>
+      <c r="T190" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12342060/pdf/</t>
+        </is>
+      </c>
+      <c r="U190" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V190" s="11" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="n">
@@ -17422,7 +19324,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7195215/</t>
         </is>
       </c>
-      <c r="T191" s="11" t="inlineStr"/>
+      <c r="T191" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7195215/pdf/</t>
+        </is>
+      </c>
+      <c r="U191" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V191" s="11" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="n">
@@ -17510,7 +19422,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5033789/</t>
         </is>
       </c>
-      <c r="T192" s="11" t="inlineStr"/>
+      <c r="T192" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5033789/pdf/</t>
+        </is>
+      </c>
+      <c r="U192" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V192" s="11" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="n">
@@ -17598,7 +19520,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12336004/</t>
         </is>
       </c>
-      <c r="T193" s="11" t="inlineStr"/>
+      <c r="T193" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12336004/pdf/</t>
+        </is>
+      </c>
+      <c r="U193" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V193" s="11" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="n">
@@ -17686,7 +19618,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12088097/</t>
         </is>
       </c>
-      <c r="T194" s="11" t="inlineStr"/>
+      <c r="T194" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12088097/pdf/</t>
+        </is>
+      </c>
+      <c r="U194" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V194" s="11" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="n">
@@ -17774,7 +19716,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6335593/</t>
         </is>
       </c>
-      <c r="T195" s="11" t="inlineStr"/>
+      <c r="T195" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6335593/pdf/</t>
+        </is>
+      </c>
+      <c r="U195" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V195" s="11" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="n">
@@ -17862,7 +19814,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7276605/</t>
         </is>
       </c>
-      <c r="T196" s="11" t="inlineStr"/>
+      <c r="T196" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7276605/pdf/</t>
+        </is>
+      </c>
+      <c r="U196" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V196" s="11" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="n">
@@ -17950,7 +19912,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10527832/</t>
         </is>
       </c>
-      <c r="T197" s="11" t="inlineStr"/>
+      <c r="T197" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10527832/pdf/</t>
+        </is>
+      </c>
+      <c r="U197" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V197" s="11" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="n">
@@ -18038,7 +20010,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4557923/</t>
         </is>
       </c>
-      <c r="T198" s="11" t="inlineStr"/>
+      <c r="T198" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4557923/pdf/</t>
+        </is>
+      </c>
+      <c r="U198" s="11" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V198" s="11" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="n">
@@ -18126,7 +20108,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6394198/</t>
         </is>
       </c>
-      <c r="T199" s="11" t="inlineStr"/>
+      <c r="T199" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6394198/pdf/</t>
+        </is>
+      </c>
+      <c r="U199" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V199" s="11" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="n">
@@ -18214,7 +20206,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10039309/</t>
         </is>
       </c>
-      <c r="T200" s="11" t="inlineStr"/>
+      <c r="T200" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10039309/pdf/</t>
+        </is>
+      </c>
+      <c r="U200" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V200" s="11" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="n">
@@ -18302,7 +20304,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13188086/</t>
         </is>
       </c>
-      <c r="T201" s="11" t="inlineStr"/>
+      <c r="T201" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13188086/pdf/</t>
+        </is>
+      </c>
+      <c r="U201" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V201" s="11" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="n">
@@ -18390,7 +20402,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5154590/</t>
         </is>
       </c>
-      <c r="T202" s="11" t="inlineStr"/>
+      <c r="T202" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5154590/pdf/</t>
+        </is>
+      </c>
+      <c r="U202" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V202" s="11" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="n">
@@ -18478,7 +20500,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4544527/</t>
         </is>
       </c>
-      <c r="T203" s="11" t="inlineStr"/>
+      <c r="T203" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4544527/pdf/</t>
+        </is>
+      </c>
+      <c r="U203" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V203" s="11" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="n">
@@ -18566,7 +20598,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9903102/</t>
         </is>
       </c>
-      <c r="T204" s="11" t="inlineStr"/>
+      <c r="T204" s="13" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9903102/pdf/</t>
+        </is>
+      </c>
+      <c r="U204" s="11" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V204" s="11" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="14" t="n">
@@ -18654,7 +20696,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10027633/</t>
         </is>
       </c>
-      <c r="T205" s="14" t="inlineStr"/>
+      <c r="T205" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10027633/pdf/</t>
+        </is>
+      </c>
+      <c r="U205" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V205" s="14" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="14" t="n">
@@ -18742,7 +20794,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9362560/</t>
         </is>
       </c>
-      <c r="T206" s="14" t="inlineStr"/>
+      <c r="T206" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9362560/pdf/</t>
+        </is>
+      </c>
+      <c r="U206" s="14" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V206" s="14" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="14" t="n">
@@ -18830,7 +20892,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9596867/</t>
         </is>
       </c>
-      <c r="T207" s="14" t="inlineStr"/>
+      <c r="T207" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9596867/pdf/</t>
+        </is>
+      </c>
+      <c r="U207" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V207" s="14" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="14" t="n">
@@ -18918,7 +20990,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13452312/</t>
         </is>
       </c>
-      <c r="T208" s="14" t="inlineStr"/>
+      <c r="T208" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13452312/pdf/</t>
+        </is>
+      </c>
+      <c r="U208" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V208" s="14" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="14" t="n">
@@ -19006,7 +21088,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3629336/</t>
         </is>
       </c>
-      <c r="T209" s="14" t="inlineStr"/>
+      <c r="T209" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3629336/pdf/</t>
+        </is>
+      </c>
+      <c r="U209" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V209" s="14" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="14" t="n">
@@ -19094,7 +21186,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12915536/</t>
         </is>
       </c>
-      <c r="T210" s="14" t="inlineStr"/>
+      <c r="T210" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12915536/pdf/</t>
+        </is>
+      </c>
+      <c r="U210" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V210" s="14" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="14" t="n">
@@ -19182,7 +21284,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5684526/</t>
         </is>
       </c>
-      <c r="T211" s="14" t="inlineStr"/>
+      <c r="T211" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5684526/pdf/</t>
+        </is>
+      </c>
+      <c r="U211" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V211" s="14" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="14" t="n">
@@ -19270,7 +21382,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12183444/</t>
         </is>
       </c>
-      <c r="T212" s="14" t="inlineStr"/>
+      <c r="T212" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12183444/pdf/</t>
+        </is>
+      </c>
+      <c r="U212" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V212" s="14" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="14" t="n">
@@ -19358,7 +21480,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12078379/</t>
         </is>
       </c>
-      <c r="T213" s="14" t="inlineStr"/>
+      <c r="T213" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12078379/pdf/</t>
+        </is>
+      </c>
+      <c r="U213" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V213" s="14" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="14" t="n">
@@ -19446,7 +21578,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7414936/</t>
         </is>
       </c>
-      <c r="T214" s="14" t="inlineStr"/>
+      <c r="T214" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7414936/pdf/</t>
+        </is>
+      </c>
+      <c r="U214" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V214" s="14" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="14" t="n">
@@ -19534,7 +21676,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12471328/</t>
         </is>
       </c>
-      <c r="T215" s="14" t="inlineStr"/>
+      <c r="T215" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12471328/pdf/</t>
+        </is>
+      </c>
+      <c r="U215" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V215" s="14" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="14" t="n">
@@ -19622,7 +21774,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13489397/</t>
         </is>
       </c>
-      <c r="T216" s="14" t="inlineStr"/>
+      <c r="T216" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13489397/pdf/</t>
+        </is>
+      </c>
+      <c r="U216" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V216" s="14" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="14" t="n">
@@ -19710,7 +21872,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11558481/</t>
         </is>
       </c>
-      <c r="T217" s="14" t="inlineStr"/>
+      <c r="T217" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11558481/pdf/</t>
+        </is>
+      </c>
+      <c r="U217" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V217" s="14" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="14" t="n">
@@ -19798,7 +21970,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8264808/</t>
         </is>
       </c>
-      <c r="T218" s="14" t="inlineStr"/>
+      <c r="T218" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8264808/pdf/</t>
+        </is>
+      </c>
+      <c r="U218" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V218" s="14" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="14" t="n">
@@ -19886,7 +22068,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8264815/</t>
         </is>
       </c>
-      <c r="T219" s="14" t="inlineStr"/>
+      <c r="T219" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8264815/pdf/</t>
+        </is>
+      </c>
+      <c r="U219" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V219" s="14" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="14" t="n">
@@ -19974,7 +22166,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6188188/</t>
         </is>
       </c>
-      <c r="T220" s="14" t="inlineStr"/>
+      <c r="T220" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6188188/pdf/</t>
+        </is>
+      </c>
+      <c r="U220" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V220" s="14" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="14" t="n">
@@ -20062,7 +22264,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13000091/</t>
         </is>
       </c>
-      <c r="T221" s="14" t="inlineStr"/>
+      <c r="T221" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13000091/pdf/</t>
+        </is>
+      </c>
+      <c r="U221" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V221" s="14" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="14" t="n">
@@ -20150,7 +22362,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8008194/</t>
         </is>
       </c>
-      <c r="T222" s="14" t="inlineStr"/>
+      <c r="T222" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8008194/pdf/</t>
+        </is>
+      </c>
+      <c r="U222" s="14" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V222" s="14" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="14" t="n">
@@ -20238,7 +22460,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10907900/</t>
         </is>
       </c>
-      <c r="T223" s="14" t="inlineStr"/>
+      <c r="T223" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10907900/pdf/</t>
+        </is>
+      </c>
+      <c r="U223" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V223" s="14" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="14" t="n">
@@ -20326,7 +22558,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9273134/</t>
         </is>
       </c>
-      <c r="T224" s="14" t="inlineStr"/>
+      <c r="T224" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9273134/pdf/</t>
+        </is>
+      </c>
+      <c r="U224" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V224" s="14" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="14" t="n">
@@ -20414,7 +22656,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8590569/</t>
         </is>
       </c>
-      <c r="T225" s="14" t="inlineStr"/>
+      <c r="T225" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8590569/pdf/</t>
+        </is>
+      </c>
+      <c r="U225" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V225" s="14" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="14" t="n">
@@ -20502,7 +22754,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9402831/</t>
         </is>
       </c>
-      <c r="T226" s="14" t="inlineStr"/>
+      <c r="T226" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9402831/pdf/</t>
+        </is>
+      </c>
+      <c r="U226" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V226" s="14" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="14" t="n">
@@ -20590,7 +22852,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11873555/</t>
         </is>
       </c>
-      <c r="T227" s="14" t="inlineStr"/>
+      <c r="T227" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11873555/pdf/</t>
+        </is>
+      </c>
+      <c r="U227" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V227" s="14" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="14" t="n">
@@ -20678,7 +22950,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10429091/</t>
         </is>
       </c>
-      <c r="T228" s="14" t="inlineStr"/>
+      <c r="T228" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10429091/pdf/</t>
+        </is>
+      </c>
+      <c r="U228" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V228" s="14" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="14" t="n">
@@ -20766,7 +23048,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10814111/</t>
         </is>
       </c>
-      <c r="T229" s="14" t="inlineStr"/>
+      <c r="T229" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10814111/pdf/</t>
+        </is>
+      </c>
+      <c r="U229" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V229" s="14" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="14" t="n">
@@ -20854,7 +23146,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10668939/</t>
         </is>
       </c>
-      <c r="T230" s="14" t="inlineStr"/>
+      <c r="T230" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10668939/pdf/</t>
+        </is>
+      </c>
+      <c r="U230" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V230" s="14" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="14" t="n">
@@ -20942,7 +23244,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10027639/</t>
         </is>
       </c>
-      <c r="T231" s="14" t="inlineStr"/>
+      <c r="T231" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10027639/pdf/</t>
+        </is>
+      </c>
+      <c r="U231" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V231" s="14" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="14" t="n">
@@ -21030,7 +23342,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7903032/</t>
         </is>
       </c>
-      <c r="T232" s="14" t="inlineStr"/>
+      <c r="T232" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7903032/pdf/</t>
+        </is>
+      </c>
+      <c r="U232" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V232" s="14" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="14" t="n">
@@ -21118,7 +23440,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3041992/</t>
         </is>
       </c>
-      <c r="T233" s="14" t="inlineStr"/>
+      <c r="T233" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3041992/pdf/</t>
+        </is>
+      </c>
+      <c r="U233" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V233" s="14" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="14" t="n">
@@ -21206,7 +23538,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11845555/</t>
         </is>
       </c>
-      <c r="T234" s="14" t="inlineStr"/>
+      <c r="T234" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11845555/pdf/</t>
+        </is>
+      </c>
+      <c r="U234" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V234" s="14" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="14" t="n">
@@ -21294,7 +23636,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6625565/</t>
         </is>
       </c>
-      <c r="T235" s="14" t="inlineStr"/>
+      <c r="T235" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6625565/pdf/</t>
+        </is>
+      </c>
+      <c r="U235" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V235" s="14" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="14" t="n">
@@ -21382,7 +23734,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8355534/</t>
         </is>
       </c>
-      <c r="T236" s="14" t="inlineStr"/>
+      <c r="T236" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8355534/pdf/</t>
+        </is>
+      </c>
+      <c r="U236" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V236" s="14" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="14" t="n">
@@ -21470,7 +23832,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9408075/</t>
         </is>
       </c>
-      <c r="T237" s="14" t="inlineStr"/>
+      <c r="T237" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9408075/pdf/</t>
+        </is>
+      </c>
+      <c r="U237" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V237" s="14" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="14" t="n">
@@ -21558,7 +23930,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13092517/</t>
         </is>
       </c>
-      <c r="T238" s="14" t="inlineStr"/>
+      <c r="T238" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13092517/pdf/</t>
+        </is>
+      </c>
+      <c r="U238" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V238" s="14" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="14" t="n">
@@ -21646,7 +24028,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5346404/</t>
         </is>
       </c>
-      <c r="T239" s="14" t="inlineStr"/>
+      <c r="T239" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5346404/pdf/</t>
+        </is>
+      </c>
+      <c r="U239" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V239" s="14" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="14" t="n">
@@ -21734,7 +24126,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12020555/</t>
         </is>
       </c>
-      <c r="T240" s="14" t="inlineStr"/>
+      <c r="T240" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12020555/pdf/</t>
+        </is>
+      </c>
+      <c r="U240" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V240" s="14" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="14" t="n">
@@ -21822,7 +24224,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6251072/</t>
         </is>
       </c>
-      <c r="T241" s="14" t="inlineStr"/>
+      <c r="T241" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6251072/pdf/</t>
+        </is>
+      </c>
+      <c r="U241" s="14" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V241" s="14" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="14" t="n">
@@ -21910,7 +24322,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6506808/</t>
         </is>
       </c>
-      <c r="T242" s="14" t="inlineStr"/>
+      <c r="T242" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6506808/pdf/</t>
+        </is>
+      </c>
+      <c r="U242" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V242" s="14" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="14" t="n">
@@ -21998,7 +24420,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9985185/</t>
         </is>
       </c>
-      <c r="T243" s="14" t="inlineStr"/>
+      <c r="T243" s="16" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9985185/pdf/</t>
+        </is>
+      </c>
+      <c r="U243" s="14" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V243" s="14" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="17" t="n">
@@ -22086,7 +24518,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3781865/</t>
         </is>
       </c>
-      <c r="T244" s="17" t="inlineStr">
+      <c r="T244" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3781865/pdf/</t>
+        </is>
+      </c>
+      <c r="U244" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V244" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -22178,7 +24620,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12952935/</t>
         </is>
       </c>
-      <c r="T245" s="17" t="inlineStr">
+      <c r="T245" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12952935/pdf/</t>
+        </is>
+      </c>
+      <c r="U245" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V245" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -22270,7 +24722,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3435893/</t>
         </is>
       </c>
-      <c r="T246" s="17" t="inlineStr">
+      <c r="T246" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3435893/pdf/</t>
+        </is>
+      </c>
+      <c r="U246" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V246" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -22362,7 +24824,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10929313/</t>
         </is>
       </c>
-      <c r="T247" s="17" t="inlineStr">
+      <c r="T247" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10929313/pdf/</t>
+        </is>
+      </c>
+      <c r="U247" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V247" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -22454,7 +24926,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8323467/</t>
         </is>
       </c>
-      <c r="T248" s="17" t="inlineStr">
+      <c r="T248" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8323467/pdf/</t>
+        </is>
+      </c>
+      <c r="U248" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V248" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -22546,7 +25028,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11989641/</t>
         </is>
       </c>
-      <c r="T249" s="17" t="inlineStr"/>
+      <c r="T249" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11989641/pdf/</t>
+        </is>
+      </c>
+      <c r="U249" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V249" s="17" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="17" t="n">
@@ -22634,7 +25126,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8811509/</t>
         </is>
       </c>
-      <c r="T250" s="17" t="inlineStr"/>
+      <c r="T250" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8811509/pdf/</t>
+        </is>
+      </c>
+      <c r="U250" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V250" s="17" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="17" t="n">
@@ -22722,7 +25224,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7929554/</t>
         </is>
       </c>
-      <c r="T251" s="17" t="inlineStr"/>
+      <c r="T251" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7929554/pdf/</t>
+        </is>
+      </c>
+      <c r="U251" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V251" s="17" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="17" t="n">
@@ -22810,7 +25322,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5367574/</t>
         </is>
       </c>
-      <c r="T252" s="17" t="inlineStr"/>
+      <c r="T252" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5367574/pdf/</t>
+        </is>
+      </c>
+      <c r="U252" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V252" s="17" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="17" t="n">
@@ -22898,7 +25420,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5496703/</t>
         </is>
       </c>
-      <c r="T253" s="17" t="inlineStr"/>
+      <c r="T253" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5496703/pdf/</t>
+        </is>
+      </c>
+      <c r="U253" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V253" s="17" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="17" t="n">
@@ -22986,7 +25518,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5682181/</t>
         </is>
       </c>
-      <c r="T254" s="17" t="inlineStr"/>
+      <c r="T254" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5682181/pdf/</t>
+        </is>
+      </c>
+      <c r="U254" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V254" s="17" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="17" t="n">
@@ -23074,7 +25616,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12093570/</t>
         </is>
       </c>
-      <c r="T255" s="17" t="inlineStr"/>
+      <c r="T255" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12093570/pdf/</t>
+        </is>
+      </c>
+      <c r="U255" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V255" s="17" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="17" t="n">
@@ -23162,7 +25714,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9718695/</t>
         </is>
       </c>
-      <c r="T256" s="17" t="inlineStr"/>
+      <c r="T256" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9718695/pdf/</t>
+        </is>
+      </c>
+      <c r="U256" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V256" s="17" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="17" t="n">
@@ -23250,7 +25812,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445125/</t>
         </is>
       </c>
-      <c r="T257" s="17" t="inlineStr">
+      <c r="T257" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445125/pdf/</t>
+        </is>
+      </c>
+      <c r="U257" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V257" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -23342,7 +25914,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5611703/</t>
         </is>
       </c>
-      <c r="T258" s="17" t="inlineStr"/>
+      <c r="T258" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5611703/pdf/</t>
+        </is>
+      </c>
+      <c r="U258" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V258" s="17" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="17" t="n">
@@ -23430,7 +26012,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445168/</t>
         </is>
       </c>
-      <c r="T259" s="17" t="inlineStr"/>
+      <c r="T259" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445168/pdf/</t>
+        </is>
+      </c>
+      <c r="U259" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V259" s="17" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="17" t="n">
@@ -23518,7 +26110,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5611704/</t>
         </is>
       </c>
-      <c r="T260" s="17" t="inlineStr"/>
+      <c r="T260" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5611704/pdf/</t>
+        </is>
+      </c>
+      <c r="U260" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V260" s="17" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="17" t="n">
@@ -23606,7 +26208,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13171015/</t>
         </is>
       </c>
-      <c r="T261" s="17" t="inlineStr"/>
+      <c r="T261" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13171015/pdf/</t>
+        </is>
+      </c>
+      <c r="U261" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V261" s="17" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="17" t="n">
@@ -23694,7 +26306,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5498094/</t>
         </is>
       </c>
-      <c r="T262" s="17" t="inlineStr"/>
+      <c r="T262" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5498094/pdf/</t>
+        </is>
+      </c>
+      <c r="U262" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V262" s="17" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="17" t="n">
@@ -23782,7 +26404,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12048364/</t>
         </is>
       </c>
-      <c r="T263" s="17" t="inlineStr"/>
+      <c r="T263" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12048364/pdf/</t>
+        </is>
+      </c>
+      <c r="U263" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V263" s="17" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="17" t="n">
@@ -23870,7 +26502,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4297050/</t>
         </is>
       </c>
-      <c r="T264" s="17" t="inlineStr"/>
+      <c r="T264" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4297050/pdf/</t>
+        </is>
+      </c>
+      <c r="U264" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V264" s="17" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="17" t="n">
@@ -23958,7 +26600,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10408344/</t>
         </is>
       </c>
-      <c r="T265" s="17" t="inlineStr"/>
+      <c r="T265" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10408344/pdf/</t>
+        </is>
+      </c>
+      <c r="U265" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V265" s="17" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="17" t="n">
@@ -24046,7 +26698,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3781874/</t>
         </is>
       </c>
-      <c r="T266" s="17" t="inlineStr"/>
+      <c r="T266" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3781874/pdf/</t>
+        </is>
+      </c>
+      <c r="U266" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V266" s="17" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="17" t="n">
@@ -24134,7 +26796,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4780668/</t>
         </is>
       </c>
-      <c r="T267" s="17" t="inlineStr"/>
+      <c r="T267" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4780668/pdf/</t>
+        </is>
+      </c>
+      <c r="U267" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V267" s="17" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="17" t="n">
@@ -24218,7 +26890,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4789926/</t>
         </is>
       </c>
-      <c r="T268" s="17" t="inlineStr"/>
+      <c r="T268" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4789926/pdf/</t>
+        </is>
+      </c>
+      <c r="U268" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V268" s="17" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="17" t="n">
@@ -24306,7 +26988,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4169618/</t>
         </is>
       </c>
-      <c r="T269" s="17" t="inlineStr"/>
+      <c r="T269" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4169618/pdf/</t>
+        </is>
+      </c>
+      <c r="U269" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V269" s="17" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="17" t="n">
@@ -24394,7 +27086,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12809027/</t>
         </is>
       </c>
-      <c r="T270" s="17" t="inlineStr"/>
+      <c r="T270" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12809027/pdf/</t>
+        </is>
+      </c>
+      <c r="U270" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V270" s="17" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="17" t="n">
@@ -24482,7 +27184,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3361354/</t>
         </is>
       </c>
-      <c r="T271" s="17" t="inlineStr">
+      <c r="T271" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3361354/pdf/</t>
+        </is>
+      </c>
+      <c r="U271" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V271" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -24574,7 +27286,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3764347/</t>
         </is>
       </c>
-      <c r="T272" s="17" t="inlineStr"/>
+      <c r="T272" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3764347/pdf/</t>
+        </is>
+      </c>
+      <c r="U272" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V272" s="17" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="17" t="n">
@@ -24662,7 +27384,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3958266/</t>
         </is>
       </c>
-      <c r="T273" s="17" t="inlineStr"/>
+      <c r="T273" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3958266/pdf/</t>
+        </is>
+      </c>
+      <c r="U273" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V273" s="17" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="17" t="n">
@@ -24750,7 +27482,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3658404/</t>
         </is>
       </c>
-      <c r="T274" s="17" t="inlineStr">
+      <c r="T274" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3658404/pdf/</t>
+        </is>
+      </c>
+      <c r="U274" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V274" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -24842,7 +27584,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6069442/</t>
         </is>
       </c>
-      <c r="T275" s="17" t="inlineStr"/>
+      <c r="T275" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6069442/pdf/</t>
+        </is>
+      </c>
+      <c r="U275" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V275" s="17" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="17" t="n">
@@ -24930,7 +27682,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9204606/</t>
         </is>
       </c>
-      <c r="T276" s="17" t="inlineStr"/>
+      <c r="T276" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9204606/pdf/</t>
+        </is>
+      </c>
+      <c r="U276" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V276" s="17" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="17" t="n">
@@ -25018,7 +27780,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5371647/</t>
         </is>
       </c>
-      <c r="T277" s="17" t="inlineStr"/>
+      <c r="T277" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5371647/pdf/</t>
+        </is>
+      </c>
+      <c r="U277" s="17" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V277" s="17" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="17" t="n">
@@ -25106,7 +27878,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3899905/</t>
         </is>
       </c>
-      <c r="T278" s="17" t="inlineStr">
+      <c r="T278" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3899905/pdf/</t>
+        </is>
+      </c>
+      <c r="U278" s="17" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V278" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -25198,7 +27980,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4556293/</t>
         </is>
       </c>
-      <c r="T279" s="17" t="inlineStr">
+      <c r="T279" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4556293/pdf/</t>
+        </is>
+      </c>
+      <c r="U279" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V279" s="17" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -25290,7 +28082,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3690728/</t>
         </is>
       </c>
-      <c r="T280" s="17" t="inlineStr"/>
+      <c r="T280" s="19" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3690728/pdf/</t>
+        </is>
+      </c>
+      <c r="U280" s="17" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V280" s="17" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="20" t="n">
@@ -25378,7 +28180,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8329314/</t>
         </is>
       </c>
-      <c r="T281" s="20" t="inlineStr"/>
+      <c r="T281" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8329314/pdf/</t>
+        </is>
+      </c>
+      <c r="U281" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V281" s="20" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="20" t="n">
@@ -25466,7 +28278,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10582256/</t>
         </is>
       </c>
-      <c r="T282" s="20" t="inlineStr"/>
+      <c r="T282" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10582256/pdf/</t>
+        </is>
+      </c>
+      <c r="U282" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V282" s="20" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="20" t="n">
@@ -25554,7 +28376,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7184218/</t>
         </is>
       </c>
-      <c r="T283" s="20" t="inlineStr"/>
+      <c r="T283" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7184218/pdf/</t>
+        </is>
+      </c>
+      <c r="U283" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V283" s="20" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="20" t="n">
@@ -25642,7 +28474,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9611820/</t>
         </is>
       </c>
-      <c r="T284" s="20" t="inlineStr"/>
+      <c r="T284" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9611820/pdf/</t>
+        </is>
+      </c>
+      <c r="U284" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V284" s="20" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="20" t="n">
@@ -25730,7 +28572,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2896576/</t>
         </is>
       </c>
-      <c r="T285" s="20" t="inlineStr"/>
+      <c r="T285" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2896576/pdf/</t>
+        </is>
+      </c>
+      <c r="U285" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V285" s="20" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="20" t="n">
@@ -25818,7 +28670,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5738151/</t>
         </is>
       </c>
-      <c r="T286" s="20" t="inlineStr"/>
+      <c r="T286" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5738151/pdf/</t>
+        </is>
+      </c>
+      <c r="U286" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V286" s="20" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="20" t="n">
@@ -25906,7 +28768,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9861410/</t>
         </is>
       </c>
-      <c r="T287" s="20" t="inlineStr"/>
+      <c r="T287" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9861410/pdf/</t>
+        </is>
+      </c>
+      <c r="U287" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V287" s="20" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="20" t="n">
@@ -25994,7 +28866,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13073083/</t>
         </is>
       </c>
-      <c r="T288" s="20" t="inlineStr"/>
+      <c r="T288" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13073083/pdf/</t>
+        </is>
+      </c>
+      <c r="U288" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V288" s="20" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="20" t="n">
@@ -26082,7 +28964,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13039414/</t>
         </is>
       </c>
-      <c r="T289" s="20" t="inlineStr"/>
+      <c r="T289" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13039414/pdf/</t>
+        </is>
+      </c>
+      <c r="U289" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V289" s="20" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="20" t="n">
@@ -26170,7 +29062,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4662984/</t>
         </is>
       </c>
-      <c r="T290" s="20" t="inlineStr"/>
+      <c r="T290" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4662984/pdf/</t>
+        </is>
+      </c>
+      <c r="U290" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V290" s="20" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="20" t="n">
@@ -26258,7 +29160,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13521579/</t>
         </is>
       </c>
-      <c r="T291" s="20" t="inlineStr"/>
+      <c r="T291" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13521579/pdf/</t>
+        </is>
+      </c>
+      <c r="U291" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V291" s="20" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="20" t="n">
@@ -26346,7 +29258,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13514819/</t>
         </is>
       </c>
-      <c r="T292" s="20" t="inlineStr"/>
+      <c r="T292" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13514819/pdf/</t>
+        </is>
+      </c>
+      <c r="U292" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V292" s="20" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="20" t="n">
@@ -26434,7 +29356,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13488007/</t>
         </is>
       </c>
-      <c r="T293" s="20" t="inlineStr"/>
+      <c r="T293" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13488007/pdf/</t>
+        </is>
+      </c>
+      <c r="U293" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V293" s="20" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="20" t="n">
@@ -26522,7 +29454,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9733235/</t>
         </is>
       </c>
-      <c r="T294" s="20" t="inlineStr"/>
+      <c r="T294" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9733235/pdf/</t>
+        </is>
+      </c>
+      <c r="U294" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V294" s="20" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="20" t="n">
@@ -26610,7 +29552,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7558520/</t>
         </is>
       </c>
-      <c r="T295" s="20" t="inlineStr"/>
+      <c r="T295" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7558520/pdf/</t>
+        </is>
+      </c>
+      <c r="U295" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V295" s="20" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="20" t="n">
@@ -26698,7 +29650,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12757876/</t>
         </is>
       </c>
-      <c r="T296" s="20" t="inlineStr"/>
+      <c r="T296" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12757876/pdf/</t>
+        </is>
+      </c>
+      <c r="U296" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V296" s="20" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="20" t="n">
@@ -26786,7 +29748,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4005904/</t>
         </is>
       </c>
-      <c r="T297" s="20" t="inlineStr"/>
+      <c r="T297" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4005904/pdf/</t>
+        </is>
+      </c>
+      <c r="U297" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V297" s="20" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="20" t="n">
@@ -26874,7 +29846,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13066407/</t>
         </is>
       </c>
-      <c r="T298" s="20" t="inlineStr"/>
+      <c r="T298" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13066407/pdf/</t>
+        </is>
+      </c>
+      <c r="U298" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V298" s="20" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="20" t="n">
@@ -26962,7 +29944,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11329135/</t>
         </is>
       </c>
-      <c r="T299" s="20" t="inlineStr"/>
+      <c r="T299" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11329135/pdf/</t>
+        </is>
+      </c>
+      <c r="U299" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V299" s="20" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="20" t="n">
@@ -27050,7 +30042,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13554579/</t>
         </is>
       </c>
-      <c r="T300" s="20" t="inlineStr"/>
+      <c r="T300" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13554579/pdf/</t>
+        </is>
+      </c>
+      <c r="U300" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V300" s="20" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="20" t="n">
@@ -27138,7 +30140,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13510065/</t>
         </is>
       </c>
-      <c r="T301" s="20" t="inlineStr"/>
+      <c r="T301" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13510065/pdf/</t>
+        </is>
+      </c>
+      <c r="U301" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V301" s="20" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="20" t="n">
@@ -27226,7 +30238,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10508267/</t>
         </is>
       </c>
-      <c r="T302" s="20" t="inlineStr"/>
+      <c r="T302" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10508267/pdf/</t>
+        </is>
+      </c>
+      <c r="U302" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V302" s="20" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="20" t="n">
@@ -27314,7 +30336,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12279651/</t>
         </is>
       </c>
-      <c r="T303" s="20" t="inlineStr"/>
+      <c r="T303" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12279651/pdf/</t>
+        </is>
+      </c>
+      <c r="U303" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V303" s="20" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="20" t="n">
@@ -27402,7 +30434,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5751726/</t>
         </is>
       </c>
-      <c r="T304" s="20" t="inlineStr"/>
+      <c r="T304" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5751726/pdf/</t>
+        </is>
+      </c>
+      <c r="U304" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V304" s="20" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="20" t="n">
@@ -27490,7 +30532,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3039607/</t>
         </is>
       </c>
-      <c r="T305" s="20" t="inlineStr"/>
+      <c r="T305" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3039607/pdf/</t>
+        </is>
+      </c>
+      <c r="U305" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V305" s="20" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="20" t="n">
@@ -27578,7 +30630,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9143587/</t>
         </is>
       </c>
-      <c r="T306" s="20" t="inlineStr"/>
+      <c r="T306" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9143587/pdf/</t>
+        </is>
+      </c>
+      <c r="U306" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V306" s="20" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="20" t="n">
@@ -27666,7 +30728,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10426640/</t>
         </is>
       </c>
-      <c r="T307" s="20" t="inlineStr"/>
+      <c r="T307" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10426640/pdf/</t>
+        </is>
+      </c>
+      <c r="U307" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V307" s="20" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="20" t="n">
@@ -27754,7 +30826,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9984160/</t>
         </is>
       </c>
-      <c r="T308" s="20" t="inlineStr"/>
+      <c r="T308" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9984160/pdf/</t>
+        </is>
+      </c>
+      <c r="U308" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V308" s="20" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="20" t="n">
@@ -27842,7 +30924,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6023437/</t>
         </is>
       </c>
-      <c r="T309" s="20" t="inlineStr">
+      <c r="T309" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6023437/pdf/</t>
+        </is>
+      </c>
+      <c r="U309" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V309" s="20" t="inlineStr">
         <is>
           <t>运动康复</t>
         </is>
@@ -27934,7 +31026,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12346195/</t>
         </is>
       </c>
-      <c r="T310" s="20" t="inlineStr"/>
+      <c r="T310" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12346195/pdf/</t>
+        </is>
+      </c>
+      <c r="U310" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V310" s="20" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="20" t="n">
@@ -28022,7 +31124,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10155853/</t>
         </is>
       </c>
-      <c r="T311" s="20" t="inlineStr"/>
+      <c r="T311" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10155853/pdf/</t>
+        </is>
+      </c>
+      <c r="U311" s="20" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V311" s="20" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="20" t="n">
@@ -28110,7 +31222,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12385555/</t>
         </is>
       </c>
-      <c r="T312" s="20" t="inlineStr"/>
+      <c r="T312" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12385555/pdf/</t>
+        </is>
+      </c>
+      <c r="U312" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V312" s="20" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="20" t="n">
@@ -28198,7 +31320,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3552977/</t>
         </is>
       </c>
-      <c r="T313" s="20" t="inlineStr"/>
+      <c r="T313" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3552977/pdf/</t>
+        </is>
+      </c>
+      <c r="U313" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V313" s="20" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="20" t="n">
@@ -28286,7 +31418,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3893395/</t>
         </is>
       </c>
-      <c r="T314" s="20" t="inlineStr"/>
+      <c r="T314" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3893395/pdf/</t>
+        </is>
+      </c>
+      <c r="U314" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V314" s="20" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="20" t="n">
@@ -28374,7 +31516,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8700844/</t>
         </is>
       </c>
-      <c r="T315" s="20" t="inlineStr"/>
+      <c r="T315" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8700844/pdf/</t>
+        </is>
+      </c>
+      <c r="U315" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V315" s="20" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="20" t="n">
@@ -28462,7 +31614,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3706243/</t>
         </is>
       </c>
-      <c r="T316" s="20" t="inlineStr"/>
+      <c r="T316" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3706243/pdf/</t>
+        </is>
+      </c>
+      <c r="U316" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V316" s="20" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="20" t="n">
@@ -28550,7 +31712,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13112255/</t>
         </is>
       </c>
-      <c r="T317" s="20" t="inlineStr"/>
+      <c r="T317" s="22" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC13112255/pdf/</t>
+        </is>
+      </c>
+      <c r="U317" s="20" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V317" s="20" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="23" t="n">
@@ -28638,7 +31810,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11297479/</t>
         </is>
       </c>
-      <c r="T318" s="23" t="inlineStr"/>
+      <c r="T318" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11297479/pdf/</t>
+        </is>
+      </c>
+      <c r="U318" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V318" s="23" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="23" t="n">
@@ -28726,7 +31908,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9528722/</t>
         </is>
       </c>
-      <c r="T319" s="23" t="inlineStr"/>
+      <c r="T319" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9528722/pdf/</t>
+        </is>
+      </c>
+      <c r="U319" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V319" s="23" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="23" t="n">
@@ -28814,7 +32006,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4718245/</t>
         </is>
       </c>
-      <c r="T320" s="23" t="inlineStr"/>
+      <c r="T320" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4718245/pdf/</t>
+        </is>
+      </c>
+      <c r="U320" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V320" s="23" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="23" t="n">
@@ -28902,7 +32104,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11065772/</t>
         </is>
       </c>
-      <c r="T321" s="23" t="inlineStr"/>
+      <c r="T321" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11065772/pdf/</t>
+        </is>
+      </c>
+      <c r="U321" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V321" s="23" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="23" t="n">
@@ -28990,7 +32202,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8805107/</t>
         </is>
       </c>
-      <c r="T322" s="23" t="inlineStr"/>
+      <c r="T322" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8805107/pdf/</t>
+        </is>
+      </c>
+      <c r="U322" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V322" s="23" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="23" t="n">
@@ -29078,7 +32300,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4647145/</t>
         </is>
       </c>
-      <c r="T323" s="23" t="inlineStr"/>
+      <c r="T323" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4647145/pdf/</t>
+        </is>
+      </c>
+      <c r="U323" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V323" s="23" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="23" t="n">
@@ -29166,7 +32398,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9456769/</t>
         </is>
       </c>
-      <c r="T324" s="23" t="inlineStr"/>
+      <c r="T324" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9456769/pdf/</t>
+        </is>
+      </c>
+      <c r="U324" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V324" s="23" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="23" t="n">
@@ -29254,7 +32496,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11784487/</t>
         </is>
       </c>
-      <c r="T325" s="23" t="inlineStr"/>
+      <c r="T325" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11784487/pdf/</t>
+        </is>
+      </c>
+      <c r="U325" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V325" s="23" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="23" t="n">
@@ -29342,7 +32594,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2684145/</t>
         </is>
       </c>
-      <c r="T326" s="23" t="inlineStr"/>
+      <c r="T326" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC2684145/pdf/</t>
+        </is>
+      </c>
+      <c r="U326" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V326" s="23" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="23" t="n">
@@ -29430,7 +32692,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8016443/</t>
         </is>
       </c>
-      <c r="T327" s="23" t="inlineStr"/>
+      <c r="T327" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8016443/pdf/</t>
+        </is>
+      </c>
+      <c r="U327" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V327" s="23" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="23" t="n">
@@ -29518,7 +32790,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12317793/</t>
         </is>
       </c>
-      <c r="T328" s="23" t="inlineStr"/>
+      <c r="T328" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12317793/pdf/</t>
+        </is>
+      </c>
+      <c r="U328" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V328" s="23" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="23" t="n">
@@ -29606,7 +32888,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11240038/</t>
         </is>
       </c>
-      <c r="T329" s="23" t="inlineStr"/>
+      <c r="T329" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC11240038/pdf/</t>
+        </is>
+      </c>
+      <c r="U329" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V329" s="23" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="23" t="n">
@@ -29694,7 +32986,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8975585/</t>
         </is>
       </c>
-      <c r="T330" s="23" t="inlineStr"/>
+      <c r="T330" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8975585/pdf/</t>
+        </is>
+      </c>
+      <c r="U330" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V330" s="23" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="23" t="n">
@@ -29782,7 +33084,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10610610/</t>
         </is>
       </c>
-      <c r="T331" s="23" t="inlineStr"/>
+      <c r="T331" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10610610/pdf/</t>
+        </is>
+      </c>
+      <c r="U331" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V331" s="23" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="23" t="n">
@@ -29870,7 +33182,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445090/</t>
         </is>
       </c>
-      <c r="T332" s="23" t="inlineStr"/>
+      <c r="T332" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445090/pdf/</t>
+        </is>
+      </c>
+      <c r="U332" s="23" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V332" s="23" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="23" t="n">
@@ -29958,7 +33280,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10407309/</t>
         </is>
       </c>
-      <c r="T333" s="23" t="inlineStr"/>
+      <c r="T333" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10407309/pdf/</t>
+        </is>
+      </c>
+      <c r="U333" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V333" s="23" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="23" t="n">
@@ -30046,7 +33378,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445080/</t>
         </is>
       </c>
-      <c r="T334" s="23" t="inlineStr"/>
+      <c r="T334" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3445080/pdf/</t>
+        </is>
+      </c>
+      <c r="U334" s="23" t="inlineStr">
+        <is>
+          <t>出版商开放获取（免费全文）</t>
+        </is>
+      </c>
+      <c r="V334" s="23" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="23" t="n">
@@ -30134,7 +33476,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12034053/</t>
         </is>
       </c>
-      <c r="T335" s="23" t="inlineStr"/>
+      <c r="T335" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12034053/pdf/</t>
+        </is>
+      </c>
+      <c r="U335" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V335" s="23" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="23" t="n">
@@ -30222,7 +33574,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4769315/</t>
         </is>
       </c>
-      <c r="T336" s="23" t="inlineStr"/>
+      <c r="T336" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4769315/pdf/</t>
+        </is>
+      </c>
+      <c r="U336" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V336" s="23" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="23" t="n">
@@ -30310,7 +33672,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7600858/</t>
         </is>
       </c>
-      <c r="T337" s="23" t="inlineStr"/>
+      <c r="T337" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7600858/pdf/</t>
+        </is>
+      </c>
+      <c r="U337" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V337" s="23" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="23" t="n">
@@ -30398,7 +33770,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6362958/</t>
         </is>
       </c>
-      <c r="T338" s="23" t="inlineStr"/>
+      <c r="T338" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6362958/pdf/</t>
+        </is>
+      </c>
+      <c r="U338" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC-ND</t>
+        </is>
+      </c>
+      <c r="V338" s="23" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="23" t="n">
@@ -30486,7 +33868,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8168984/</t>
         </is>
       </c>
-      <c r="T339" s="23" t="inlineStr"/>
+      <c r="T339" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8168984/pdf/</t>
+        </is>
+      </c>
+      <c r="U339" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA</t>
+        </is>
+      </c>
+      <c r="V339" s="23" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="23" t="n">
@@ -30574,7 +33966,17 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7739583/</t>
         </is>
       </c>
-      <c r="T340" s="23" t="inlineStr"/>
+      <c r="T340" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7739583/pdf/</t>
+        </is>
+      </c>
+      <c r="U340" s="23" t="inlineStr">
+        <is>
+          <t>CC BY</t>
+        </is>
+      </c>
+      <c r="V340" s="23" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="23" t="n">
@@ -30662,691 +34064,1041 @@
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12317788/</t>
         </is>
       </c>
-      <c r="T341" s="23" t="inlineStr"/>
+      <c r="T341" s="25" t="inlineStr">
+        <is>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12317788/pdf/</t>
+        </is>
+      </c>
+      <c r="U341" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-NC</t>
+        </is>
+      </c>
+      <c r="V341" s="23" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T341"/>
+  <autoFilter ref="A1:V341"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S188" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S190" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S205" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S206" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S207" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S208" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S209" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S210" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S211" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S212" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S213" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S214" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S215" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S216" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S217" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S218" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S219" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S220" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S221" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S222" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S223" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S225" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S226" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S227" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S228" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S229" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S231" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S232" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S233" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S239" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S257" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S266" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S267" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P268" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S268" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S269" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S270" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S271" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P272" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S272" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P273" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S273" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P274" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S274" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P275" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S275" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P276" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S276" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P277" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S277" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P278" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S278" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P279" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S279" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P280" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S280" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P281" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S281" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P282" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S282" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P283" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S283" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P284" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S284" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P285" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S285" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P286" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S286" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P287" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S287" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S288" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P289" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S289" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P290" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S290" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P291" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S291" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P292" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S292" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P293" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S293" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P294" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S294" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P295" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S295" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P296" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S296" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P297" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S297" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P298" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S298" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P299" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S299" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P300" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S300" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P301" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S301" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P302" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S302" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P303" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S303" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P304" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S304" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P305" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S305" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P306" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S306" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P307" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S307" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P308" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S308" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P309" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S309" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P310" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S310" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P311" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S311" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P312" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S312" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P313" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S313" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P314" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S314" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P315" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S315" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P316" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S316" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P317" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S317" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P318" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S318" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P319" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S319" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P320" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S320" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P321" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S321" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P322" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S322" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P323" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S323" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P324" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S324" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P325" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S325" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P326" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S326" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P327" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S327" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P328" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S328" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P329" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S329" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P330" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S330" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P331" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S331" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P332" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S332" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P333" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S333" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P334" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S334" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P335" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S335" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P336" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S336" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P337" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S337" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P338" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S338" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P339" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S339" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P340" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S340" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P341" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S341" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T45" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T46" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T47" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T51" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T52" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T53" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T54" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P55" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T55" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P56" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T56" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T57" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T58" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T59" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T60" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P61" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T61" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P62" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T62" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P63" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T63" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P64" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T64" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P65" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T65" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T66" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P67" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T67" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P68" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T68" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T69" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T70" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P71" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T71" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P72" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T72" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P73" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S73" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T73" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P74" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S74" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T74" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P75" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S75" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T75" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P76" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S76" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T76" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P77" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S77" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T77" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P78" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T78" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P79" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T79" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P80" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T80" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T81" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T82" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P83" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S83" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T83" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P84" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S84" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T84" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S85" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T85" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S86" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T86" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S87" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T87" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P88" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S88" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T88" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S89" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T89" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P90" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S90" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T90" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S91" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T91" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T92" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P93" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T93" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T94" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S95" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T95" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P96" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S96" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T96" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P97" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T97" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P98" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T98" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P99" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S99" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T99" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P100" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S100" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T100" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P101" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S101" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T101" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P102" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S102" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T102" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P103" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T103" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P104" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T104" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P105" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T105" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P106" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T106" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P107" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T107" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P108" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T108" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P109" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T109" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P110" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T110" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P111" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T111" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P112" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T112" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P113" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T113" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T114" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S115" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T115" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S116" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T116" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S117" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T117" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P118" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S118" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T118" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P119" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S119" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T119" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S120" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T120" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S121" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T121" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S122" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T122" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S123" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T123" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P124" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S124" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T124" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S125" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T125" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S126" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T126" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S127" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T127" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S128" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T128" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P129" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S129" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T129" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P130" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S130" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T130" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S131" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T131" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T132" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S133" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T133" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S134" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T134" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P135" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S135" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T135" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P136" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T136" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P137" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S137" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T137" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P138" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S138" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T138" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P139" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S139" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T139" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P140" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S140" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T140" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S141" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T141" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S142" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T142" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S143" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T143" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S144" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T144" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P145" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S145" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T145" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P146" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S146" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T146" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S147" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T147" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S148" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T148" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S149" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T149" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S150" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T150" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S151" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T151" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S152" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T152" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S153" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T153" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S154" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T154" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P155" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S155" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T155" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P156" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S156" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T156" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P157" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S157" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T157" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P158" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S158" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T158" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P159" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S159" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T159" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P160" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S160" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T160" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P161" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S161" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T161" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P162" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S162" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T162" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P163" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S163" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T163" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P164" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S164" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T164" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P165" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S165" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T165" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P166" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S166" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T166" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P167" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S167" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T167" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P168" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S168" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T168" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P169" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S169" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T169" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P170" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S170" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T170" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P171" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S171" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T171" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P172" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S172" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T172" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P173" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S173" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T173" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P174" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S174" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T174" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P175" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S175" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T175" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P176" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S176" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T176" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P177" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S177" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T177" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P178" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S178" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T178" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P179" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S179" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T179" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P180" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S180" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T180" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P181" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S181" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T181" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P182" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S182" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T182" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P183" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S183" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T183" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P184" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S184" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T184" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P185" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S185" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T185" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P186" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S186" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T186" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P187" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S187" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T187" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P188" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S188" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T188" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P189" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S189" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T189" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P190" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S190" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T190" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P191" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S191" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T191" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P192" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S192" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T192" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P193" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S193" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T193" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P194" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S194" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T194" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P195" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S195" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T195" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P196" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S196" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T196" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P197" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S197" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T197" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P198" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S198" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T198" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P199" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S199" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T199" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P200" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S200" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T200" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P201" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S201" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T201" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P202" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S202" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T202" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P203" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S203" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T203" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P204" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S204" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T204" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P205" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S205" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T205" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P206" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S206" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T206" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P207" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S207" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T207" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P208" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S208" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T208" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P209" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S209" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T209" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P210" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S210" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T210" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P211" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S211" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T211" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P212" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S212" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T212" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P213" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S213" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T213" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P214" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S214" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T214" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P215" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S215" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T215" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P216" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S216" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T216" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P217" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S217" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T217" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P218" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S218" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T218" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P219" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S219" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T219" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P220" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S220" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T220" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P221" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S221" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T221" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P222" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S222" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T222" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P223" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S223" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T223" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P224" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S224" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T224" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P225" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S225" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T225" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P226" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S226" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T226" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P227" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S227" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T227" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P228" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S228" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T228" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P229" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S229" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T229" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P230" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S230" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T230" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P231" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S231" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T231" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P232" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S232" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T232" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P233" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S233" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T233" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P234" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S234" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T234" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P235" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S235" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T235" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P236" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S236" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T236" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P237" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S237" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T237" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P238" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S238" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T238" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P239" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S239" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T239" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P240" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S240" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T240" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P241" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S241" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T241" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P242" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S242" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T242" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P243" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S243" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T243" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P244" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S244" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T244" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P245" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S245" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T245" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P246" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S246" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T246" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P247" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S247" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T247" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P248" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S248" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T248" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P249" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S249" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T249" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P250" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S250" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T250" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P251" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S251" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T251" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P252" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S252" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T252" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P253" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S253" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T253" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P254" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S254" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T254" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P255" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S255" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T255" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P256" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S256" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T256" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P257" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S257" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T257" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P258" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S258" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T258" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P259" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S259" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T259" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P260" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S260" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T260" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P261" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S261" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T261" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P262" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S262" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T262" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P263" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S263" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T263" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P264" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S264" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T264" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P265" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S265" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T265" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P266" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S266" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T266" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P267" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S267" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T267" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P268" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S268" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T268" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P269" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S269" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T269" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P270" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S270" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T270" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P271" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S271" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T271" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P272" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S272" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T272" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P273" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S273" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T273" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P274" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S274" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T274" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P275" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S275" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T275" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P276" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S276" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T276" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P277" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S277" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T277" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P278" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S278" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T278" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P279" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S279" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T279" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P280" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S280" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T280" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P281" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S281" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T281" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P282" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S282" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T282" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P283" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S283" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T283" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P284" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S284" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T284" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P285" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S285" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T285" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P286" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S286" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T286" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P287" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S287" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T287" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P288" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S288" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T288" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P289" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S289" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T289" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P290" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S290" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T290" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P291" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S291" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T291" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P292" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S292" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T292" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P293" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S293" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T293" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P294" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S294" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T294" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P295" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S295" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T295" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P296" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S296" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T296" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P297" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S297" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T297" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P298" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S298" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T298" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P299" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S299" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T299" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P300" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S300" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T300" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P301" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S301" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T301" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P302" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S302" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T302" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P303" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S303" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T303" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P304" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S304" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T304" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P305" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S305" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T305" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P306" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S306" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T306" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P307" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S307" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T307" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P308" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S308" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T308" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P309" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S309" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T309" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P310" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S310" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T310" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P311" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S311" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T311" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P312" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S312" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T312" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P313" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S313" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T313" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P314" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S314" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T314" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P315" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S315" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T315" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P316" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S316" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T316" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P317" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S317" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T317" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P318" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S318" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T318" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P319" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S319" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T319" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P320" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S320" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T320" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P321" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S321" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T321" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P322" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S322" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T322" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P323" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S323" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T323" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P324" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S324" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T324" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P325" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S325" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T325" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P326" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S326" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T326" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P327" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S327" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T327" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P328" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S328" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T328" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P329" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S329" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T329" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P330" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S330" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T330" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P331" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S331" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T331" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P332" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S332" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T332" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P333" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S333" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T333" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P334" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S334" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T334" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P335" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S335" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T335" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P336" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S336" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T336" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P337" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S337" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T337" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P338" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S338" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T338" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P339" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S339" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T339" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P340" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S340" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T340" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P341" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S341" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T341" r:id="rId1020"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31712,7 +35464,7 @@
     <row r="2">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>1. 来源：Europe PMC / PubMed Central 开放获取全文（全部可免费下载 PDF），辅以全网检索定位权威文章。</t>
+          <t>1. 来源：全部 340 篇均为开放获取（Europe PMC 标记 isOpenAccess=Y，且收录于 PubMed Central），可免费阅读全文并下载 PDF；许可证：CC BY 143 篇、CC BY-NC 70 篇、CC BY-NC-ND 87 篇、CC BY-NC-SA 17 篇，另 23 篇（Sports Health 17、J Ultrason 3 等）为出版商开放获取、未标 CC 许可。PDF 下载列点开即跳转到 PMC 的 PDF 文件。</t>
         </is>
       </c>
     </row>
